--- a/Templates/BOMLibrary.xlsx
+++ b/Templates/BOMLibrary.xlsx
@@ -1,36 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HW\Altium Lib\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Hardware\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4C1598-68CB-4E0A-B6DF-FA07B116F423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C63A92-9E56-4A8C-8F69-FAD78E845A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="-120" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Component list</t>
   </si>
@@ -96,6 +121,12 @@
   </si>
   <si>
     <t>Column=Description</t>
+  </si>
+  <si>
+    <t>Column=Part Number</t>
+  </si>
+  <si>
+    <t>Column=Fitted</t>
   </si>
 </sst>
 </file>
@@ -105,7 +136,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,12 +155,6 @@
       <color indexed="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="13"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -373,19 +398,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -448,68 +460,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -517,92 +532,105 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -621,59 +649,68 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1628775</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>82021</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Resim 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6797F5BE-A48C-B2FC-BDD2-4DCBA09D9E30}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11906250" y="609600"/>
-          <a:ext cx="1266825" cy="1196446"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -947,258 +984,264 @@
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="26.5703125" customWidth="1"/>
+    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="28"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
+      <c r="A1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31" t="s">
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="26" t="s">
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="29"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10" t="s">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="51"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="52" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="29"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="4"/>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="12" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="52"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="53"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="29"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="14" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="52"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="53"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="5"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="52"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="53"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="52"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="53"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17">
         <f ca="1">NOW()</f>
-        <v>44775.884173726852</v>
-      </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="52"/>
+        <v>46087.498214467596</v>
+      </c>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="53"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="23" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="25"/>
+      <c r="J9" s="20" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="41">
+      <c r="A10" s="23"/>
+      <c r="B10" s="35">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="40"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="34"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="42">
+      <c r="A11" s="23"/>
+      <c r="B11" s="36">
         <f>ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="40"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="34"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="43">
+      <c r="A12" s="23"/>
+      <c r="B12" s="37">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="40"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="34"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="49" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="50"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46" t="s">
+      <c r="D13" s="40"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="55"/>
-      <c r="I13" s="47"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="35" t="s">
+      <c r="A14" s="23"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="29"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="56"/>
+      <c r="I14" s="47"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="36"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="56"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="36"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="56"/>
+      <c r="I16" s="43"/>
       <c r="J16" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="57"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1208,6 +1251,5 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>